--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty Alpha Low - Volatility 30 ETF FOF.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty Alpha Low - Volatility 30 ETF FOF.xlsx
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Nifty Alpha Low - Volatility 30 ETF FOF</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -79,7 +79,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -885,10 +885,10 @@
         <v>12</v>
       </c>
       <c r="F5" s="9">
-        <v>87789.11</v>
+        <v>95240.49</v>
       </c>
       <c r="G5" s="10">
-        <v>0.9982218290759</v>
+        <v>0.9993511173181</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>12</v>
@@ -908,13 +908,13 @@
         <v>15</v>
       </c>
       <c r="E6" s="14">
-        <v>327083139</v>
+        <v>350020177</v>
       </c>
       <c r="F6" s="15">
-        <v>87789.11</v>
+        <v>95240.49</v>
       </c>
       <c r="G6" s="16">
-        <v>0.9982218290759</v>
+        <v>0.9993511173181</v>
       </c>
       <c r="H6" s="15" t="s">
         <v>12</v>
@@ -945,10 +945,10 @@
         <v>12</v>
       </c>
       <c r="F8" s="9">
-        <v>266.75</v>
+        <v>207.25</v>
       </c>
       <c r="G8" s="10">
-        <v>0.0030331287434</v>
+        <v>0.0021746582683</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>12</v>
@@ -979,10 +979,10 @@
         <v>12</v>
       </c>
       <c r="F10" s="18">
-        <v>-110.36788301999331</v>
+        <v>-145.40996850001102</v>
       </c>
       <c r="G10" s="19">
-        <v>-0.0012549578194774138</v>
+        <v>-0.001525775586514507</v>
       </c>
       <c r="H10" s="18" t="s">
         <v>12</v>
@@ -1005,10 +1005,10 @@
         <v>12</v>
       </c>
       <c r="F11" s="18">
-        <v>87945.49211698</v>
+        <v>95302.3300315</v>
       </c>
       <c r="G11" s="19">
-        <v>0.9999999999998226</v>
+        <v>0.9999999999998855</v>
       </c>
       <c r="H11" s="18" t="s">
         <v>12</v>
